--- a/soap-sales-plan.xlsx
+++ b/soap-sales-plan.xlsx
@@ -1708,24 +1708,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B26"/>
     <mergeCell ref="A28:D28"/>
-    <mergeCell ref="B21"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A30:D30"/>
-    <mergeCell ref="B25"/>
-    <mergeCell ref="B24"/>
-    <mergeCell ref="B20"/>
-    <mergeCell ref="B22"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B23"/>
-    <mergeCell ref="B27"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="طريقة العمولة" error="اختر موحدة أو حسب المنتج" type="list">
